--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91584</v>
+        <v>91590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91590</v>
+        <v>91594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91596</v>
+        <v>91609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91611</v>
+        <v>91614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91614</v>
+        <v>91624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91625</v>
+        <v>91628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91630</v>
+        <v>91635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91635</v>
+        <v>91647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91648</v>
+        <v>91651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33291-2026 artfynd.xlsx
+++ b/artfynd/A 33291-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137043621</v>
       </c>
       <c r="B2" t="n">
-        <v>91651</v>
+        <v>91655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137043620</v>
       </c>
       <c r="B3" t="n">
-        <v>108211</v>
+        <v>108217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
